--- a/src/assets/plantilla-vymc.xlsx
+++ b/src/assets/plantilla-vymc.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/44ef21c77d26af9f/Escritorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="176" documentId="13_ncr:1_{4EFF9419-0B38-4164-BC40-D6F6F6A47E84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB5D990E-1B74-4A51-8855-5D5924DD74F1}"/>
+  <xr:revisionPtr revIDLastSave="204" documentId="13_ncr:1_{4EFF9419-0B38-4164-BC40-D6F6F6A47E84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3428ED3-2A2C-4DB6-953E-9616E785F833}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,55 +25,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="47">
   <si>
     <t>Lectura semanal de la Biblia:</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="11"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>●</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">Palabras de introd. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color indexed="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>(1 min)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>:</t>
-    </r>
-  </si>
-  <si>
     <t>TESOROS DE LA BIBLIA</t>
   </si>
   <si>
@@ -84,33 +40,6 @@
   </si>
   <si>
     <t>Lector:</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="16"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">● </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">Palabras de conclusión </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color indexed="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>(3 min)</t>
-    </r>
   </si>
   <si>
     <t>2. Busquemos perlas escondidas(10 mins.)</t>
@@ -230,34 +159,6 @@
     <t>JEREMÍAS 20, 21</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="11"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>●</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>Canción 73 y oración:</t>
-    </r>
-  </si>
-  <si>
     <t>SEMANA</t>
   </si>
   <si>
@@ -338,24 +239,6 @@
   </si>
   <si>
     <t>3. Lectura de la Biblia (4 mins.)</t>
-  </si>
-  <si>
-    <t>● Canción y oración:</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">● </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Canción  y oración</t>
-    </r>
   </si>
   <si>
     <r>
@@ -459,6 +342,30 @@
   <si>
     <t>Responsable</t>
   </si>
+  <si>
+    <t>● Canción: xx</t>
+  </si>
+  <si>
+    <t>Oración:</t>
+  </si>
+  <si>
+    <t>Oración final:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">● </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Canción  xx</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -489,12 +396,6 @@
     <font>
       <sz val="8"/>
       <color indexed="8"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="11"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -651,6 +552,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -696,7 +603,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="59">
+  <borders count="52">
     <border>
       <left/>
       <right/>
@@ -902,59 +809,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF505050"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF505050"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="8"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF505050"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="8"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF505050"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF505050"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF505050"/>
       </left>
@@ -1256,17 +1110,6 @@
       </left>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color rgb="FF505050"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
       <bottom style="thin">
         <color rgb="FF505050"/>
       </bottom>
@@ -1281,19 +1124,6 @@
         <color rgb="FF505050"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF505050"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1348,7 +1178,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="205">
+  <cellXfs count="182">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1357,31 +1187,31 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1397,55 +1227,50 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1457,338 +1282,302 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="9" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="21" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="9" fillId="6" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="29" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="45" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="31" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="5" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="20" fontId="6" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="22" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="30" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="10" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="30" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="31" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="32" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="50" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1885,8 +1674,8 @@
       <xdr:rowOff>80141</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>642257</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>674915</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>102829</xdr:rowOff>
     </xdr:to>
@@ -1922,6 +1711,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3002,12 +2795,12 @@
   <dimension ref="A4:L109"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.21875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16" style="1" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.21875" style="1" customWidth="1"/>
     <col min="4" max="4" width="11.33203125" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.44140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.77734375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="22.5546875" style="1" customWidth="1"/>
     <col min="7" max="7" width="31.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.109375" style="1" customWidth="1"/>
     <col min="9" max="9" width="11.88671875" style="1" customWidth="1"/>
@@ -3017,336 +2810,338 @@
   <sheetData>
     <row r="4" spans="1:10" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="5" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="196"/>
-      <c r="B5" s="197"/>
-      <c r="C5" s="197"/>
-      <c r="D5" s="197"/>
-      <c r="E5" s="197"/>
-      <c r="F5" s="197"/>
-      <c r="G5" s="197"/>
-      <c r="H5" s="197"/>
-      <c r="I5" s="198"/>
+      <c r="A5" s="107"/>
+      <c r="B5" s="108"/>
+      <c r="C5" s="108"/>
+      <c r="D5" s="108"/>
+      <c r="E5" s="108"/>
+      <c r="F5" s="108"/>
+      <c r="G5" s="108"/>
+      <c r="H5" s="108"/>
+      <c r="I5" s="109"/>
       <c r="J5" s="19"/>
     </row>
     <row r="6" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="199"/>
-      <c r="B6" s="195"/>
-      <c r="C6" s="195"/>
-      <c r="D6" s="195"/>
-      <c r="E6" s="195"/>
-      <c r="F6" s="195"/>
-      <c r="G6" s="195"/>
-      <c r="H6" s="195"/>
-      <c r="I6" s="200"/>
+      <c r="A6" s="110"/>
+      <c r="B6" s="106"/>
+      <c r="C6" s="106"/>
+      <c r="D6" s="106"/>
+      <c r="E6" s="106"/>
+      <c r="F6" s="106"/>
+      <c r="G6" s="106"/>
+      <c r="H6" s="106"/>
+      <c r="I6" s="111"/>
       <c r="J6" s="19"/>
     </row>
     <row r="7" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="199"/>
-      <c r="B7" s="195"/>
-      <c r="C7" s="195"/>
-      <c r="D7" s="195"/>
-      <c r="E7" s="195"/>
-      <c r="F7" s="195"/>
-      <c r="G7" s="195"/>
-      <c r="H7" s="195"/>
-      <c r="I7" s="200"/>
+      <c r="A7" s="110"/>
+      <c r="B7" s="106"/>
+      <c r="C7" s="106"/>
+      <c r="D7" s="106"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="106"/>
+      <c r="G7" s="106"/>
+      <c r="H7" s="106"/>
+      <c r="I7" s="111"/>
       <c r="J7" s="19"/>
     </row>
     <row r="8" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="199"/>
-      <c r="B8" s="195"/>
-      <c r="C8" s="195"/>
-      <c r="D8" s="195"/>
-      <c r="E8" s="195"/>
-      <c r="F8" s="195"/>
-      <c r="G8" s="195"/>
-      <c r="H8" s="195"/>
-      <c r="I8" s="200"/>
+      <c r="A8" s="110"/>
+      <c r="B8" s="106"/>
+      <c r="C8" s="106"/>
+      <c r="D8" s="106"/>
+      <c r="E8" s="106"/>
+      <c r="F8" s="106"/>
+      <c r="G8" s="106"/>
+      <c r="H8" s="106"/>
+      <c r="I8" s="111"/>
       <c r="J8" s="19"/>
     </row>
     <row r="9" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="199"/>
-      <c r="B9" s="195"/>
-      <c r="C9" s="195"/>
-      <c r="D9" s="195"/>
-      <c r="E9" s="195"/>
-      <c r="F9" s="195"/>
-      <c r="G9" s="195"/>
-      <c r="H9" s="195"/>
-      <c r="I9" s="200"/>
+      <c r="A9" s="110"/>
+      <c r="B9" s="106"/>
+      <c r="C9" s="106"/>
+      <c r="D9" s="106"/>
+      <c r="E9" s="106"/>
+      <c r="F9" s="106"/>
+      <c r="G9" s="106"/>
+      <c r="H9" s="106"/>
+      <c r="I9" s="111"/>
       <c r="J9" s="19"/>
     </row>
     <row r="10" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="199"/>
-      <c r="B10" s="195"/>
-      <c r="C10" s="195"/>
-      <c r="D10" s="195"/>
-      <c r="E10" s="195"/>
-      <c r="F10" s="195"/>
-      <c r="G10" s="195"/>
-      <c r="H10" s="195"/>
-      <c r="I10" s="200"/>
+      <c r="A10" s="110"/>
+      <c r="B10" s="106"/>
+      <c r="C10" s="106"/>
+      <c r="D10" s="106"/>
+      <c r="E10" s="106"/>
+      <c r="F10" s="106"/>
+      <c r="G10" s="106"/>
+      <c r="H10" s="106"/>
+      <c r="I10" s="111"/>
       <c r="J10" s="19"/>
     </row>
     <row r="11" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="199"/>
-      <c r="B11" s="195"/>
-      <c r="C11" s="195"/>
-      <c r="D11" s="195"/>
-      <c r="E11" s="195"/>
-      <c r="F11" s="195"/>
-      <c r="G11" s="195"/>
-      <c r="H11" s="195"/>
-      <c r="I11" s="200"/>
+      <c r="A11" s="110"/>
+      <c r="B11" s="106"/>
+      <c r="C11" s="106"/>
+      <c r="D11" s="106"/>
+      <c r="E11" s="106"/>
+      <c r="F11" s="106"/>
+      <c r="G11" s="106"/>
+      <c r="H11" s="106"/>
+      <c r="I11" s="111"/>
       <c r="J11" s="19"/>
     </row>
     <row r="12" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="199"/>
-      <c r="B12" s="195"/>
-      <c r="C12" s="195"/>
-      <c r="D12" s="195"/>
-      <c r="E12" s="195"/>
-      <c r="F12" s="195"/>
-      <c r="G12" s="195"/>
-      <c r="H12" s="195"/>
-      <c r="I12" s="200"/>
+      <c r="A12" s="110"/>
+      <c r="B12" s="106"/>
+      <c r="C12" s="106"/>
+      <c r="D12" s="106"/>
+      <c r="E12" s="106"/>
+      <c r="F12" s="106"/>
+      <c r="G12" s="106"/>
+      <c r="H12" s="106"/>
+      <c r="I12" s="111"/>
       <c r="J12" s="19"/>
     </row>
     <row r="13" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="199"/>
-      <c r="B13" s="195"/>
-      <c r="C13" s="195"/>
-      <c r="D13" s="195"/>
-      <c r="E13" s="195"/>
-      <c r="F13" s="195"/>
-      <c r="G13" s="195"/>
-      <c r="H13" s="195"/>
-      <c r="I13" s="200"/>
+      <c r="A13" s="110"/>
+      <c r="B13" s="106"/>
+      <c r="C13" s="106"/>
+      <c r="D13" s="106"/>
+      <c r="E13" s="106"/>
+      <c r="F13" s="106"/>
+      <c r="G13" s="106"/>
+      <c r="H13" s="106"/>
+      <c r="I13" s="111"/>
       <c r="J13" s="19"/>
     </row>
     <row r="14" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A14" s="201"/>
-      <c r="B14" s="202"/>
-      <c r="C14" s="202"/>
-      <c r="D14" s="203"/>
-      <c r="E14" s="203"/>
-      <c r="F14" s="203"/>
-      <c r="G14" s="203"/>
-      <c r="H14" s="203"/>
-      <c r="I14" s="204"/>
+      <c r="A14" s="112"/>
+      <c r="B14" s="113"/>
+      <c r="C14" s="113"/>
+      <c r="D14" s="114"/>
+      <c r="E14" s="114"/>
+      <c r="F14" s="114"/>
+      <c r="G14" s="114"/>
+      <c r="H14" s="114"/>
+      <c r="I14" s="115"/>
       <c r="J14" s="19"/>
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="166" t="s">
-        <v>9</v>
+      <c r="A15" s="91" t="s">
+        <v>7</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="5"/>
       <c r="D15" s="8"/>
-      <c r="E15" s="59"/>
+      <c r="E15" s="54"/>
       <c r="F15" s="12"/>
-      <c r="G15" s="60" t="s">
+      <c r="G15" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="H15" s="61" t="s">
-        <v>10</v>
-      </c>
-      <c r="I15" s="167"/>
+      <c r="H15" s="56" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" s="92"/>
       <c r="J15" s="19"/>
     </row>
     <row r="16" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="129" t="s">
-        <v>41</v>
-      </c>
-      <c r="B16" s="97"/>
-      <c r="C16" s="75"/>
-      <c r="D16" s="98"/>
-      <c r="E16" s="92" t="s">
+      <c r="A16" s="178" t="s">
         <v>43</v>
       </c>
-      <c r="F16" s="93"/>
-      <c r="G16" s="94"/>
-      <c r="H16" s="75"/>
-      <c r="I16" s="137"/>
+      <c r="B16" s="179" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="122"/>
+      <c r="D16" s="141"/>
+      <c r="E16" s="138" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" s="139"/>
+      <c r="G16" s="140"/>
+      <c r="H16" s="122"/>
+      <c r="I16" s="123"/>
       <c r="J16" s="19"/>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="117" t="s">
+      <c r="A17" s="134" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" s="135"/>
+      <c r="C17" s="135"/>
+      <c r="D17" s="135"/>
+      <c r="E17" s="135"/>
+      <c r="F17" s="135"/>
+      <c r="G17" s="135"/>
+      <c r="H17" s="135"/>
+      <c r="I17" s="136"/>
+      <c r="J17" s="19"/>
+    </row>
+    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="73" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="36"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="37"/>
+      <c r="H18" s="137"/>
+      <c r="I18" s="125"/>
+      <c r="J18" s="19"/>
+    </row>
+    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="73" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="37"/>
+      <c r="H19" s="132"/>
+      <c r="I19" s="121"/>
+      <c r="J19" s="19"/>
+    </row>
+    <row r="20" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="73" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="122"/>
+      <c r="I20" s="123"/>
+      <c r="J20" s="19"/>
+    </row>
+    <row r="21" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="143" t="s">
         <v>2</v>
       </c>
-      <c r="B17" s="118"/>
-      <c r="C17" s="118"/>
-      <c r="D17" s="118"/>
-      <c r="E17" s="118"/>
-      <c r="F17" s="118"/>
-      <c r="G17" s="118"/>
-      <c r="H17" s="118"/>
-      <c r="I17" s="119"/>
-      <c r="J17" s="19"/>
-    </row>
-    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="135" t="s">
+      <c r="B21" s="144"/>
+      <c r="C21" s="144"/>
+      <c r="D21" s="144"/>
+      <c r="E21" s="144"/>
+      <c r="F21" s="144"/>
+      <c r="G21" s="144"/>
+      <c r="H21" s="144"/>
+      <c r="I21" s="145"/>
+      <c r="J21" s="19"/>
+    </row>
+    <row r="22" spans="1:10" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="74" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="39"/>
-      <c r="C18" s="39"/>
-      <c r="D18" s="39"/>
-      <c r="E18" s="110"/>
-      <c r="F18" s="107"/>
-      <c r="G18" s="40"/>
-      <c r="H18" s="79"/>
-      <c r="I18" s="134"/>
-      <c r="J18" s="19"/>
-    </row>
-    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="135" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="39"/>
-      <c r="C19" s="39"/>
-      <c r="D19" s="39"/>
-      <c r="E19" s="110"/>
-      <c r="F19" s="107"/>
-      <c r="G19" s="40"/>
-      <c r="H19" s="72"/>
-      <c r="I19" s="136"/>
-      <c r="J19" s="19"/>
-    </row>
-    <row r="20" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="39"/>
-      <c r="C20" s="39"/>
-      <c r="D20" s="41"/>
-      <c r="E20" s="110"/>
-      <c r="F20" s="107"/>
-      <c r="G20" s="43"/>
-      <c r="H20" s="75"/>
-      <c r="I20" s="137"/>
-      <c r="J20" s="19"/>
-    </row>
-    <row r="21" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="114" t="s">
-        <v>3</v>
-      </c>
-      <c r="B21" s="115"/>
-      <c r="C21" s="115"/>
-      <c r="D21" s="115"/>
-      <c r="E21" s="115"/>
-      <c r="F21" s="115"/>
-      <c r="G21" s="115"/>
-      <c r="H21" s="115"/>
-      <c r="I21" s="116"/>
-      <c r="J21" s="19"/>
-    </row>
-    <row r="22" spans="1:10" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="140" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" s="46"/>
-      <c r="C22" s="46"/>
-      <c r="D22" s="46"/>
-      <c r="E22" s="46"/>
-      <c r="F22" s="46"/>
-      <c r="G22" s="113" t="s">
-        <v>47</v>
-      </c>
-      <c r="H22" s="70"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="H22" s="150"/>
       <c r="I22" s="130"/>
       <c r="J22" s="19"/>
     </row>
     <row r="23" spans="1:10" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="168"/>
-      <c r="B23" s="31"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="111"/>
-      <c r="F23" s="111"/>
-      <c r="G23" s="112" t="s">
-        <v>46</v>
-      </c>
-      <c r="H23" s="70"/>
-      <c r="I23" s="169"/>
+      <c r="A23" s="93"/>
+      <c r="B23" s="28"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="142"/>
+      <c r="F23" s="142"/>
+      <c r="G23" s="61" t="s">
+        <v>41</v>
+      </c>
+      <c r="H23" s="150"/>
+      <c r="I23" s="172"/>
       <c r="J23" s="19"/>
     </row>
     <row r="24" spans="1:10" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="140" t="s">
-        <v>29</v>
-      </c>
-      <c r="B24" s="33"/>
-      <c r="C24" s="33"/>
-      <c r="D24" s="34"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="33"/>
-      <c r="G24" s="113" t="s">
-        <v>47</v>
-      </c>
-      <c r="H24" s="84"/>
-      <c r="I24" s="170"/>
+      <c r="A24" s="74" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="30"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="31"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="H24" s="118"/>
+      <c r="I24" s="154"/>
       <c r="J24" s="19"/>
     </row>
     <row r="25" spans="1:10" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="141"/>
-      <c r="B25" s="35"/>
-      <c r="C25" s="35"/>
-      <c r="D25" s="36"/>
-      <c r="E25" s="105"/>
-      <c r="F25" s="106"/>
-      <c r="G25" s="112" t="s">
-        <v>46</v>
-      </c>
-      <c r="H25" s="70"/>
+      <c r="A25" s="75"/>
+      <c r="B25" s="32"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="43"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="61" t="s">
+        <v>41</v>
+      </c>
+      <c r="H25" s="150"/>
       <c r="I25" s="130"/>
       <c r="J25" s="19"/>
     </row>
     <row r="26" spans="1:10" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="143" t="s">
-        <v>30</v>
-      </c>
-      <c r="B26" s="37"/>
-      <c r="C26" s="37"/>
-      <c r="D26" s="38"/>
-      <c r="E26" s="48"/>
-      <c r="F26" s="37"/>
-      <c r="G26" s="113" t="s">
-        <v>47</v>
-      </c>
-      <c r="H26" s="84"/>
-      <c r="I26" s="170"/>
+      <c r="A26" s="76" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="34"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="34"/>
+      <c r="G26" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="H26" s="118"/>
+      <c r="I26" s="154"/>
       <c r="J26" s="19"/>
     </row>
     <row r="27" spans="1:10" ht="14.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="141"/>
-      <c r="B27" s="35"/>
-      <c r="C27" s="35"/>
-      <c r="D27" s="36"/>
-      <c r="E27" s="105"/>
-      <c r="F27" s="106"/>
-      <c r="G27" s="112" t="s">
-        <v>46</v>
-      </c>
-      <c r="H27" s="70"/>
+      <c r="A27" s="75"/>
+      <c r="B27" s="32"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="43"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="61" t="s">
+        <v>41</v>
+      </c>
+      <c r="H27" s="150"/>
       <c r="I27" s="130"/>
       <c r="J27" s="19"/>
     </row>
     <row r="28" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="145" t="s">
-        <v>4</v>
-      </c>
-      <c r="B28" s="80"/>
-      <c r="C28" s="80"/>
-      <c r="D28" s="80"/>
-      <c r="E28" s="80"/>
-      <c r="F28" s="80"/>
-      <c r="G28" s="80"/>
-      <c r="H28" s="80"/>
-      <c r="I28" s="146"/>
+      <c r="A28" s="166" t="s">
+        <v>3</v>
+      </c>
+      <c r="B28" s="167"/>
+      <c r="C28" s="167"/>
+      <c r="D28" s="167"/>
+      <c r="E28" s="167"/>
+      <c r="F28" s="167"/>
+      <c r="G28" s="167"/>
+      <c r="H28" s="167"/>
+      <c r="I28" s="168"/>
       <c r="J28" s="19"/>
     </row>
     <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="147" t="s">
-        <v>11</v>
+      <c r="A29" s="77" t="s">
+        <v>9</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -3355,282 +3150,286 @@
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
       <c r="H29" s="8"/>
-      <c r="I29" s="148"/>
+      <c r="I29" s="78"/>
       <c r="J29" s="19"/>
     </row>
     <row r="30" spans="1:10" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="150" t="s">
-        <v>33</v>
-      </c>
-      <c r="B30" s="44"/>
-      <c r="C30" s="44"/>
+      <c r="A30" s="80" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" s="41"/>
+      <c r="C30" s="41"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
       <c r="G30" s="3"/>
-      <c r="H30" s="72"/>
-      <c r="I30" s="136"/>
+      <c r="H30" s="132"/>
+      <c r="I30" s="121"/>
       <c r="J30" s="19"/>
     </row>
     <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="149" t="s">
-        <v>8</v>
-      </c>
-      <c r="B31" s="44"/>
-      <c r="C31" s="44"/>
+      <c r="A31" s="79" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="41"/>
+      <c r="C31" s="41"/>
       <c r="D31" s="3"/>
-      <c r="E31" s="72"/>
-      <c r="F31" s="91"/>
-      <c r="G31" s="57" t="s">
+      <c r="E31" s="132"/>
+      <c r="F31" s="133"/>
+      <c r="G31" s="52" t="s">
+        <v>4</v>
+      </c>
+      <c r="H31" s="132"/>
+      <c r="I31" s="121"/>
+      <c r="J31" s="19"/>
+    </row>
+    <row r="32" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="105" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="81"/>
+      <c r="C32" s="81"/>
+      <c r="D32" s="81"/>
+      <c r="E32" s="82"/>
+      <c r="F32" s="180" t="s">
+        <v>46</v>
+      </c>
+      <c r="G32" s="181" t="s">
+        <v>45</v>
+      </c>
+      <c r="H32" s="157"/>
+      <c r="I32" s="158"/>
+      <c r="J32" s="19"/>
+    </row>
+    <row r="33" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="94"/>
+      <c r="B33" s="83"/>
+      <c r="C33" s="83"/>
+      <c r="D33" s="83"/>
+      <c r="E33" s="83"/>
+      <c r="F33" s="83"/>
+      <c r="G33" s="83"/>
+      <c r="H33" s="83"/>
+      <c r="I33" s="95"/>
+    </row>
+    <row r="34" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="B34" s="64"/>
+      <c r="C34" s="65"/>
+      <c r="D34" s="66"/>
+      <c r="E34" s="67"/>
+      <c r="F34" s="68"/>
+      <c r="G34" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="H34" s="70" t="s">
+        <v>15</v>
+      </c>
+      <c r="I34" s="71"/>
+      <c r="J34" s="19"/>
+    </row>
+    <row r="35" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="178" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" s="179" t="s">
+        <v>44</v>
+      </c>
+      <c r="C35" s="122"/>
+      <c r="D35" s="141"/>
+      <c r="E35" s="138" t="s">
+        <v>38</v>
+      </c>
+      <c r="F35" s="139"/>
+      <c r="G35" s="140"/>
+      <c r="H35" s="122"/>
+      <c r="I35" s="123"/>
+      <c r="J35" s="19"/>
+    </row>
+    <row r="36" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="146" t="s">
+        <v>1</v>
+      </c>
+      <c r="B36" s="147"/>
+      <c r="C36" s="147"/>
+      <c r="D36" s="147"/>
+      <c r="E36" s="147"/>
+      <c r="F36" s="147"/>
+      <c r="G36" s="147"/>
+      <c r="H36" s="147"/>
+      <c r="I36" s="148"/>
+      <c r="J36" s="19"/>
+    </row>
+    <row r="37" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="72" t="s">
+        <v>22</v>
+      </c>
+      <c r="B37" s="36"/>
+      <c r="C37" s="36"/>
+      <c r="D37" s="36"/>
+      <c r="E37" s="36"/>
+      <c r="F37" s="36"/>
+      <c r="G37" s="37"/>
+      <c r="H37" s="155"/>
+      <c r="I37" s="125"/>
+      <c r="J37" s="19"/>
+    </row>
+    <row r="38" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="H31" s="72"/>
-      <c r="I31" s="136"/>
-      <c r="J31" s="19"/>
-    </row>
-    <row r="32" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="171" t="s">
-        <v>6</v>
-      </c>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="63" t="s">
+      <c r="B38" s="36"/>
+      <c r="C38" s="36"/>
+      <c r="D38" s="36"/>
+      <c r="E38" s="36"/>
+      <c r="F38" s="36"/>
+      <c r="G38" s="37"/>
+      <c r="H38" s="156"/>
+      <c r="I38" s="121"/>
+      <c r="J38" s="19"/>
+    </row>
+    <row r="39" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="B39" s="36"/>
+      <c r="C39" s="36"/>
+      <c r="D39" s="38"/>
+      <c r="E39" s="39"/>
+      <c r="F39" s="39"/>
+      <c r="G39" s="46"/>
+      <c r="H39" s="149"/>
+      <c r="I39" s="123"/>
+      <c r="J39" s="19"/>
+    </row>
+    <row r="40" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="126" t="s">
+        <v>2</v>
+      </c>
+      <c r="B40" s="127"/>
+      <c r="C40" s="127"/>
+      <c r="D40" s="127"/>
+      <c r="E40" s="127"/>
+      <c r="F40" s="127"/>
+      <c r="G40" s="127"/>
+      <c r="H40" s="127"/>
+      <c r="I40" s="128"/>
+      <c r="J40" s="19"/>
+    </row>
+    <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="B41" s="30"/>
+      <c r="C41" s="30"/>
+      <c r="D41" s="42"/>
+      <c r="E41" s="43"/>
+      <c r="F41" s="30"/>
+      <c r="G41" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="H32" s="96"/>
-      <c r="I32" s="172"/>
-      <c r="J32" s="19"/>
-    </row>
-    <row r="33" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="173"/>
-      <c r="B33" s="158"/>
-      <c r="C33" s="158"/>
-      <c r="D33" s="158"/>
-      <c r="E33" s="158"/>
-      <c r="F33" s="158"/>
-      <c r="G33" s="158"/>
-      <c r="H33" s="158"/>
-      <c r="I33" s="174"/>
-    </row>
-    <row r="34" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="120" t="s">
-        <v>12</v>
-      </c>
-      <c r="B34" s="121"/>
-      <c r="C34" s="122"/>
-      <c r="D34" s="123"/>
-      <c r="E34" s="124"/>
-      <c r="F34" s="125"/>
-      <c r="G34" s="126" t="s">
-        <v>0</v>
-      </c>
-      <c r="H34" s="127" t="s">
-        <v>17</v>
-      </c>
-      <c r="I34" s="128"/>
-      <c r="J34" s="19"/>
-    </row>
-    <row r="35" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="129" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="97"/>
-      <c r="C35" s="85"/>
-      <c r="D35" s="71"/>
-      <c r="E35" s="99" t="s">
-        <v>1</v>
-      </c>
-      <c r="F35" s="100"/>
-      <c r="G35" s="101"/>
-      <c r="H35" s="85"/>
-      <c r="I35" s="130"/>
-      <c r="J35" s="19"/>
-    </row>
-    <row r="36" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="131" t="s">
-        <v>2</v>
-      </c>
-      <c r="B36" s="95"/>
-      <c r="C36" s="95"/>
-      <c r="D36" s="95"/>
-      <c r="E36" s="95"/>
-      <c r="F36" s="95"/>
-      <c r="G36" s="95"/>
-      <c r="H36" s="95"/>
-      <c r="I36" s="132"/>
-      <c r="J36" s="19"/>
-    </row>
-    <row r="37" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="133" t="s">
-        <v>25</v>
-      </c>
-      <c r="B37" s="39"/>
-      <c r="C37" s="39"/>
-      <c r="D37" s="39"/>
-      <c r="E37" s="39"/>
-      <c r="F37" s="39"/>
-      <c r="G37" s="40"/>
-      <c r="H37" s="103"/>
-      <c r="I37" s="134"/>
-      <c r="J37" s="19"/>
-    </row>
-    <row r="38" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="135" t="s">
-        <v>7</v>
-      </c>
-      <c r="B38" s="39"/>
-      <c r="C38" s="39"/>
-      <c r="D38" s="39"/>
-      <c r="E38" s="39"/>
-      <c r="F38" s="39"/>
-      <c r="G38" s="40"/>
-      <c r="H38" s="82"/>
-      <c r="I38" s="136"/>
-      <c r="J38" s="19"/>
-    </row>
-    <row r="39" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="135" t="s">
-        <v>13</v>
-      </c>
-      <c r="B39" s="39"/>
-      <c r="C39" s="39"/>
-      <c r="D39" s="41"/>
-      <c r="E39" s="42"/>
-      <c r="F39" s="42"/>
-      <c r="G39" s="49"/>
-      <c r="H39" s="102"/>
-      <c r="I39" s="137"/>
-      <c r="J39" s="19"/>
-    </row>
-    <row r="40" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="138" t="s">
-        <v>3</v>
-      </c>
-      <c r="B40" s="74"/>
-      <c r="C40" s="74"/>
-      <c r="D40" s="74"/>
-      <c r="E40" s="74"/>
-      <c r="F40" s="74"/>
-      <c r="G40" s="74"/>
-      <c r="H40" s="74"/>
-      <c r="I40" s="139"/>
-      <c r="J40" s="19"/>
-    </row>
-    <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="140" t="s">
-        <v>28</v>
-      </c>
-      <c r="B41" s="33"/>
-      <c r="C41" s="33"/>
-      <c r="D41" s="45"/>
-      <c r="E41" s="46"/>
-      <c r="F41" s="33"/>
-      <c r="G41" s="113" t="s">
-        <v>47</v>
-      </c>
-      <c r="H41" s="85"/>
+      <c r="H41" s="129"/>
       <c r="I41" s="130"/>
       <c r="J41" s="19"/>
     </row>
     <row r="42" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="141"/>
-      <c r="B42" s="35"/>
-      <c r="C42" s="35"/>
-      <c r="D42" s="36"/>
-      <c r="E42" s="105"/>
-      <c r="F42" s="105"/>
-      <c r="G42" s="112" t="s">
-        <v>46</v>
-      </c>
-      <c r="H42" s="86"/>
-      <c r="I42" s="142"/>
+      <c r="A42" s="75"/>
+      <c r="B42" s="32"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="33"/>
+      <c r="E42" s="43"/>
+      <c r="F42" s="43"/>
+      <c r="G42" s="61" t="s">
+        <v>41</v>
+      </c>
+      <c r="H42" s="165"/>
+      <c r="I42" s="173"/>
       <c r="J42" s="19"/>
     </row>
     <row r="43" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="143" t="s">
-        <v>31</v>
-      </c>
-      <c r="B43" s="37"/>
-      <c r="C43" s="37"/>
-      <c r="D43" s="47"/>
-      <c r="E43" s="48"/>
-      <c r="F43" s="37"/>
-      <c r="G43" s="113" t="s">
-        <v>47</v>
-      </c>
-      <c r="H43" s="85"/>
+      <c r="A43" s="76" t="s">
+        <v>28</v>
+      </c>
+      <c r="B43" s="34"/>
+      <c r="C43" s="34"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="45"/>
+      <c r="F43" s="34"/>
+      <c r="G43" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="H43" s="129"/>
       <c r="I43" s="130"/>
       <c r="J43" s="19"/>
     </row>
     <row r="44" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="141"/>
-      <c r="B44" s="35"/>
-      <c r="C44" s="35"/>
-      <c r="D44" s="36"/>
-      <c r="E44" s="105"/>
-      <c r="F44" s="106"/>
-      <c r="G44" s="112" t="s">
-        <v>46</v>
-      </c>
-      <c r="H44" s="86"/>
-      <c r="I44" s="144"/>
+      <c r="A44" s="75"/>
+      <c r="B44" s="32"/>
+      <c r="C44" s="32"/>
+      <c r="D44" s="33"/>
+      <c r="E44" s="43"/>
+      <c r="F44" s="30"/>
+      <c r="G44" s="61" t="s">
+        <v>41</v>
+      </c>
+      <c r="H44" s="165"/>
+      <c r="I44" s="117"/>
       <c r="J44" s="19"/>
     </row>
     <row r="45" spans="1:12" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="143" t="s">
-        <v>32</v>
-      </c>
-      <c r="B45" s="37"/>
-      <c r="C45" s="37"/>
-      <c r="D45" s="47"/>
-      <c r="E45" s="48"/>
-      <c r="F45" s="37"/>
-      <c r="G45" s="113" t="s">
-        <v>47</v>
-      </c>
-      <c r="H45" s="85"/>
+      <c r="A45" s="76" t="s">
+        <v>29</v>
+      </c>
+      <c r="B45" s="34"/>
+      <c r="C45" s="34"/>
+      <c r="D45" s="44"/>
+      <c r="E45" s="45"/>
+      <c r="F45" s="34"/>
+      <c r="G45" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="H45" s="129"/>
       <c r="I45" s="130"/>
       <c r="J45" s="19"/>
       <c r="K45" s="19"/>
     </row>
     <row r="46" spans="1:12" ht="14.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="141"/>
-      <c r="B46" s="35"/>
-      <c r="C46" s="35"/>
-      <c r="D46" s="36"/>
-      <c r="E46" s="105"/>
-      <c r="F46" s="106"/>
-      <c r="G46" s="112" t="s">
-        <v>46</v>
-      </c>
-      <c r="H46" s="70"/>
+      <c r="A46" s="75"/>
+      <c r="B46" s="32"/>
+      <c r="C46" s="32"/>
+      <c r="D46" s="33"/>
+      <c r="E46" s="43"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="61" t="s">
+        <v>41</v>
+      </c>
+      <c r="H46" s="150"/>
       <c r="I46" s="130"/>
-      <c r="J46" s="65"/>
-      <c r="K46" s="66"/>
+      <c r="J46" s="174"/>
+      <c r="K46" s="169"/>
       <c r="L46" s="19"/>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="145" t="s">
-        <v>4</v>
-      </c>
-      <c r="B47" s="80"/>
-      <c r="C47" s="80"/>
-      <c r="D47" s="80"/>
-      <c r="E47" s="80"/>
-      <c r="F47" s="80"/>
-      <c r="G47" s="80"/>
-      <c r="H47" s="80"/>
-      <c r="I47" s="146"/>
-      <c r="J47" s="65"/>
-      <c r="K47" s="66"/>
+      <c r="A47" s="166" t="s">
+        <v>3</v>
+      </c>
+      <c r="B47" s="167"/>
+      <c r="C47" s="167"/>
+      <c r="D47" s="167"/>
+      <c r="E47" s="167"/>
+      <c r="F47" s="167"/>
+      <c r="G47" s="167"/>
+      <c r="H47" s="167"/>
+      <c r="I47" s="168"/>
+      <c r="J47" s="174"/>
+      <c r="K47" s="169"/>
       <c r="L47" s="19"/>
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="147" t="s">
-        <v>14</v>
+      <c r="A48" s="77" t="s">
+        <v>12</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -3639,75 +3438,77 @@
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
       <c r="H48" s="8"/>
-      <c r="I48" s="148"/>
-      <c r="J48" s="65"/>
-      <c r="K48" s="66"/>
+      <c r="I48" s="78"/>
+      <c r="J48" s="174"/>
+      <c r="K48" s="169"/>
       <c r="L48" s="19"/>
     </row>
     <row r="49" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="149" t="s">
-        <v>33</v>
-      </c>
-      <c r="B49" s="44"/>
-      <c r="C49" s="44"/>
-      <c r="D49" s="44"/>
+      <c r="A49" s="79" t="s">
+        <v>30</v>
+      </c>
+      <c r="B49" s="41"/>
+      <c r="C49" s="41"/>
+      <c r="D49" s="41"/>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
       <c r="G49" s="3"/>
-      <c r="H49" s="82"/>
-      <c r="I49" s="136"/>
-      <c r="J49" s="65"/>
-      <c r="K49" s="66"/>
+      <c r="H49" s="156"/>
+      <c r="I49" s="121"/>
+      <c r="J49" s="174"/>
+      <c r="K49" s="169"/>
       <c r="L49" s="19"/>
     </row>
     <row r="50" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="150" t="s">
-        <v>36</v>
-      </c>
-      <c r="B50" s="44"/>
-      <c r="C50" s="44"/>
-      <c r="D50" s="50"/>
-      <c r="E50" s="82"/>
-      <c r="F50" s="73"/>
-      <c r="G50" s="57" t="s">
-        <v>5</v>
-      </c>
-      <c r="H50" s="82"/>
-      <c r="I50" s="136"/>
+      <c r="A50" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="B50" s="41"/>
+      <c r="C50" s="41"/>
+      <c r="D50" s="47"/>
+      <c r="E50" s="156"/>
+      <c r="F50" s="177"/>
+      <c r="G50" s="52" t="s">
+        <v>4</v>
+      </c>
+      <c r="H50" s="156"/>
+      <c r="I50" s="121"/>
       <c r="J50" s="19"/>
       <c r="K50" s="19"/>
     </row>
     <row r="51" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="151" t="s">
-        <v>6</v>
-      </c>
-      <c r="B51" s="152"/>
-      <c r="C51" s="152"/>
-      <c r="D51" s="152"/>
-      <c r="E51" s="153"/>
-      <c r="F51" s="154"/>
-      <c r="G51" s="155" t="s">
-        <v>42</v>
-      </c>
-      <c r="H51" s="156"/>
-      <c r="I51" s="157"/>
+      <c r="A51" s="105" t="s">
+        <v>39</v>
+      </c>
+      <c r="B51" s="81"/>
+      <c r="C51" s="81"/>
+      <c r="D51" s="81"/>
+      <c r="E51" s="82"/>
+      <c r="F51" s="180" t="s">
+        <v>46</v>
+      </c>
+      <c r="G51" s="181" t="s">
+        <v>45</v>
+      </c>
+      <c r="H51" s="157"/>
+      <c r="I51" s="158"/>
       <c r="J51" s="19"/>
     </row>
     <row r="52" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="175"/>
-      <c r="B52" s="158"/>
-      <c r="C52" s="158"/>
-      <c r="D52" s="158"/>
-      <c r="E52" s="158"/>
-      <c r="F52" s="159"/>
-      <c r="G52" s="160"/>
-      <c r="H52" s="161"/>
-      <c r="I52" s="176"/>
+      <c r="A52" s="96"/>
+      <c r="B52" s="83"/>
+      <c r="C52" s="83"/>
+      <c r="D52" s="83"/>
+      <c r="E52" s="83"/>
+      <c r="F52" s="84"/>
+      <c r="G52" s="85"/>
+      <c r="H52" s="86"/>
+      <c r="I52" s="97"/>
       <c r="J52" s="19"/>
     </row>
     <row r="53" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="177" t="s">
-        <v>15</v>
+      <c r="A53" s="98" t="s">
+        <v>13</v>
       </c>
       <c r="B53" s="22"/>
       <c r="C53" s="23"/>
@@ -3717,45 +3518,47 @@
       <c r="G53" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="H53" s="51" t="s">
-        <v>16</v>
-      </c>
-      <c r="I53" s="178"/>
+      <c r="H53" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="I53" s="99"/>
       <c r="J53" s="19"/>
     </row>
     <row r="54" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="129" t="s">
-        <v>41</v>
-      </c>
-      <c r="B54" s="97"/>
-      <c r="C54" s="83"/>
-      <c r="D54" s="98"/>
-      <c r="E54" s="92" t="s">
+      <c r="A54" s="178" t="s">
         <v>43</v>
       </c>
-      <c r="F54" s="93"/>
-      <c r="G54" s="94"/>
-      <c r="H54" s="83"/>
-      <c r="I54" s="137"/>
+      <c r="B54" s="179" t="s">
+        <v>44</v>
+      </c>
+      <c r="C54" s="122"/>
+      <c r="D54" s="141"/>
+      <c r="E54" s="138" t="s">
+        <v>38</v>
+      </c>
+      <c r="F54" s="139"/>
+      <c r="G54" s="140"/>
+      <c r="H54" s="122"/>
+      <c r="I54" s="123"/>
       <c r="J54" s="19"/>
     </row>
     <row r="55" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="131" t="s">
-        <v>2</v>
-      </c>
-      <c r="B55" s="95"/>
-      <c r="C55" s="95"/>
-      <c r="D55" s="95"/>
-      <c r="E55" s="95"/>
-      <c r="F55" s="95"/>
-      <c r="G55" s="95"/>
-      <c r="H55" s="95"/>
-      <c r="I55" s="132"/>
+      <c r="A55" s="146" t="s">
+        <v>1</v>
+      </c>
+      <c r="B55" s="147"/>
+      <c r="C55" s="147"/>
+      <c r="D55" s="147"/>
+      <c r="E55" s="147"/>
+      <c r="F55" s="147"/>
+      <c r="G55" s="147"/>
+      <c r="H55" s="147"/>
+      <c r="I55" s="148"/>
       <c r="J55" s="19"/>
     </row>
     <row r="56" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="135" t="s">
-        <v>25</v>
+      <c r="A56" s="73" t="s">
+        <v>22</v>
       </c>
       <c r="B56" s="19"/>
       <c r="C56" s="2"/>
@@ -3763,13 +3566,13 @@
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
       <c r="G56" s="3"/>
-      <c r="H56" s="78"/>
-      <c r="I56" s="134"/>
+      <c r="H56" s="124"/>
+      <c r="I56" s="125"/>
       <c r="J56" s="19"/>
     </row>
     <row r="57" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="135" t="s">
-        <v>35</v>
+      <c r="A57" s="73" t="s">
+        <v>32</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -3777,13 +3580,13 @@
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
       <c r="G57" s="3"/>
-      <c r="H57" s="90"/>
-      <c r="I57" s="136"/>
+      <c r="H57" s="120"/>
+      <c r="I57" s="121"/>
       <c r="J57" s="19"/>
     </row>
     <row r="58" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="135" t="s">
-        <v>34</v>
+      <c r="A58" s="73" t="s">
+        <v>31</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -3791,131 +3594,131 @@
       <c r="E58" s="14"/>
       <c r="F58" s="14"/>
       <c r="G58" s="6"/>
-      <c r="H58" s="83"/>
-      <c r="I58" s="137"/>
+      <c r="H58" s="151"/>
+      <c r="I58" s="123"/>
       <c r="J58" s="19"/>
     </row>
     <row r="59" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="138" t="s">
-        <v>3</v>
-      </c>
-      <c r="B59" s="74"/>
-      <c r="C59" s="74"/>
-      <c r="D59" s="74"/>
-      <c r="E59" s="74"/>
-      <c r="F59" s="74"/>
-      <c r="G59" s="74"/>
-      <c r="H59" s="74"/>
-      <c r="I59" s="139"/>
+      <c r="A59" s="126" t="s">
+        <v>2</v>
+      </c>
+      <c r="B59" s="127"/>
+      <c r="C59" s="127"/>
+      <c r="D59" s="127"/>
+      <c r="E59" s="127"/>
+      <c r="F59" s="127"/>
+      <c r="G59" s="127"/>
+      <c r="H59" s="127"/>
+      <c r="I59" s="128"/>
       <c r="J59" s="19"/>
     </row>
     <row r="60" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="179" t="s">
-        <v>38</v>
+      <c r="A60" s="100" t="s">
+        <v>35</v>
       </c>
       <c r="B60" s="7"/>
       <c r="C60" s="7"/>
       <c r="D60" s="15"/>
       <c r="E60" s="14"/>
       <c r="F60" s="14"/>
-      <c r="G60" s="113" t="s">
-        <v>47</v>
-      </c>
-      <c r="H60" s="81"/>
+      <c r="G60" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="H60" s="152"/>
       <c r="I60" s="130"/>
       <c r="J60" s="19"/>
     </row>
     <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="141"/>
+      <c r="A61" s="75"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
       <c r="D61" s="13"/>
-      <c r="E61" s="107"/>
-      <c r="F61" s="107"/>
-      <c r="G61" s="112" t="s">
-        <v>46</v>
-      </c>
-      <c r="H61" s="81"/>
+      <c r="E61" s="14"/>
+      <c r="F61" s="14"/>
+      <c r="G61" s="61" t="s">
+        <v>41</v>
+      </c>
+      <c r="H61" s="152"/>
       <c r="I61" s="130"/>
       <c r="J61" s="19"/>
     </row>
     <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="180" t="s">
-        <v>31</v>
+      <c r="A62" s="101" t="s">
+        <v>28</v>
       </c>
       <c r="B62" s="20"/>
       <c r="C62" s="20"/>
       <c r="D62" s="21"/>
-      <c r="E62" s="104"/>
-      <c r="F62" s="104"/>
-      <c r="G62" s="113" t="s">
-        <v>47</v>
-      </c>
-      <c r="H62" s="69"/>
-      <c r="I62" s="170"/>
+      <c r="E62" s="131"/>
+      <c r="F62" s="131"/>
+      <c r="G62" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="H62" s="153"/>
+      <c r="I62" s="154"/>
       <c r="J62" s="19"/>
     </row>
     <row r="63" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="141"/>
+      <c r="A63" s="75"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
       <c r="D63" s="13"/>
-      <c r="E63" s="107"/>
-      <c r="F63" s="107"/>
-      <c r="G63" s="112" t="s">
-        <v>46</v>
-      </c>
-      <c r="H63" s="81"/>
+      <c r="E63" s="14"/>
+      <c r="F63" s="14"/>
+      <c r="G63" s="61" t="s">
+        <v>41</v>
+      </c>
+      <c r="H63" s="152"/>
       <c r="I63" s="130"/>
       <c r="J63" s="19"/>
     </row>
     <row r="64" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="180" t="s">
-        <v>32</v>
+      <c r="A64" s="101" t="s">
+        <v>29</v>
       </c>
       <c r="B64" s="20"/>
       <c r="C64" s="20"/>
       <c r="D64" s="21"/>
-      <c r="E64" s="53"/>
-      <c r="F64" s="53"/>
-      <c r="G64" s="113" t="s">
-        <v>47</v>
-      </c>
-      <c r="H64" s="69"/>
-      <c r="I64" s="170"/>
+      <c r="E64" s="50"/>
+      <c r="F64" s="50"/>
+      <c r="G64" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="H64" s="153"/>
+      <c r="I64" s="154"/>
       <c r="J64" s="19"/>
     </row>
     <row r="65" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="141"/>
+      <c r="A65" s="75"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
       <c r="D65" s="13"/>
-      <c r="E65" s="107"/>
-      <c r="F65" s="107"/>
-      <c r="G65" s="112" t="s">
-        <v>46</v>
-      </c>
-      <c r="H65" s="81"/>
+      <c r="E65" s="14"/>
+      <c r="F65" s="14"/>
+      <c r="G65" s="61" t="s">
+        <v>41</v>
+      </c>
+      <c r="H65" s="152"/>
       <c r="I65" s="130"/>
       <c r="J65" s="19"/>
     </row>
     <row r="66" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="145" t="s">
-        <v>4</v>
-      </c>
-      <c r="B66" s="80"/>
-      <c r="C66" s="80"/>
-      <c r="D66" s="80"/>
-      <c r="E66" s="80"/>
-      <c r="F66" s="80"/>
-      <c r="G66" s="80"/>
-      <c r="H66" s="80"/>
-      <c r="I66" s="146"/>
+      <c r="A66" s="166" t="s">
+        <v>3</v>
+      </c>
+      <c r="B66" s="167"/>
+      <c r="C66" s="167"/>
+      <c r="D66" s="167"/>
+      <c r="E66" s="167"/>
+      <c r="F66" s="167"/>
+      <c r="G66" s="167"/>
+      <c r="H66" s="167"/>
+      <c r="I66" s="168"/>
       <c r="J66" s="19"/>
     </row>
     <row r="67" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="147" t="s">
-        <v>18</v>
+      <c r="A67" s="77" t="s">
+        <v>16</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -3924,70 +3727,72 @@
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
       <c r="H67" s="8"/>
-      <c r="I67" s="148"/>
+      <c r="I67" s="78"/>
       <c r="J67" s="19"/>
     </row>
     <row r="68" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="150" t="s">
-        <v>33</v>
-      </c>
-      <c r="B68" s="62"/>
-      <c r="C68" s="62"/>
-      <c r="D68" s="62"/>
-      <c r="E68" s="62"/>
+      <c r="A68" s="80" t="s">
+        <v>30</v>
+      </c>
+      <c r="B68" s="57"/>
+      <c r="C68" s="57"/>
+      <c r="D68" s="57"/>
+      <c r="E68" s="57"/>
       <c r="F68" s="2"/>
       <c r="G68" s="3"/>
-      <c r="H68" s="90"/>
-      <c r="I68" s="136"/>
+      <c r="H68" s="120"/>
+      <c r="I68" s="121"/>
       <c r="J68" s="19"/>
     </row>
     <row r="69" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="149" t="s">
-        <v>8</v>
+      <c r="A69" s="79" t="s">
+        <v>6</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
-      <c r="E69" s="76"/>
-      <c r="F69" s="77"/>
+      <c r="E69" s="170"/>
+      <c r="F69" s="176"/>
       <c r="G69" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="H69" s="78"/>
-      <c r="I69" s="134"/>
+        <v>4</v>
+      </c>
+      <c r="H69" s="124"/>
+      <c r="I69" s="125"/>
       <c r="J69" s="19"/>
     </row>
     <row r="70" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="181" t="s">
-        <v>44</v>
-      </c>
-      <c r="B70" s="28"/>
-      <c r="C70" s="28"/>
-      <c r="D70" s="28"/>
-      <c r="E70" s="28"/>
-      <c r="F70" s="54"/>
-      <c r="G70" s="63" t="s">
-        <v>42</v>
-      </c>
-      <c r="H70" s="87"/>
-      <c r="I70" s="172"/>
+      <c r="A70" s="105" t="s">
+        <v>39</v>
+      </c>
+      <c r="B70" s="81"/>
+      <c r="C70" s="81"/>
+      <c r="D70" s="81"/>
+      <c r="E70" s="82"/>
+      <c r="F70" s="180" t="s">
+        <v>46</v>
+      </c>
+      <c r="G70" s="181" t="s">
+        <v>45</v>
+      </c>
+      <c r="H70" s="157"/>
+      <c r="I70" s="158"/>
       <c r="J70" s="19"/>
     </row>
     <row r="71" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="175"/>
-      <c r="B71" s="158"/>
-      <c r="C71" s="158"/>
-      <c r="D71" s="158"/>
-      <c r="E71" s="158"/>
-      <c r="F71" s="159"/>
-      <c r="G71" s="160"/>
-      <c r="H71" s="162"/>
-      <c r="I71" s="176"/>
+      <c r="A71" s="96"/>
+      <c r="B71" s="83"/>
+      <c r="C71" s="83"/>
+      <c r="D71" s="83"/>
+      <c r="E71" s="83"/>
+      <c r="F71" s="84"/>
+      <c r="G71" s="85"/>
+      <c r="H71" s="87"/>
+      <c r="I71" s="97"/>
       <c r="J71" s="19"/>
     </row>
     <row r="72" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="182" t="s">
-        <v>19</v>
+      <c r="A72" s="102" t="s">
+        <v>17</v>
       </c>
       <c r="B72" s="22"/>
       <c r="C72" s="23"/>
@@ -3997,45 +3802,47 @@
       <c r="G72" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="H72" s="64" t="s">
-        <v>20</v>
-      </c>
-      <c r="I72" s="178"/>
+      <c r="H72" s="58" t="s">
+        <v>18</v>
+      </c>
+      <c r="I72" s="99"/>
       <c r="J72" s="19"/>
     </row>
     <row r="73" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="183" t="s">
-        <v>21</v>
-      </c>
-      <c r="B73" s="101"/>
-      <c r="C73" s="75"/>
-      <c r="D73" s="98"/>
-      <c r="E73" s="92" t="s">
+      <c r="A73" s="178" t="s">
         <v>43</v>
       </c>
-      <c r="F73" s="93"/>
-      <c r="G73" s="94"/>
-      <c r="H73" s="75"/>
-      <c r="I73" s="137"/>
+      <c r="B73" s="179" t="s">
+        <v>44</v>
+      </c>
+      <c r="C73" s="122"/>
+      <c r="D73" s="141"/>
+      <c r="E73" s="138" t="s">
+        <v>38</v>
+      </c>
+      <c r="F73" s="139"/>
+      <c r="G73" s="140"/>
+      <c r="H73" s="122"/>
+      <c r="I73" s="123"/>
       <c r="J73" s="19"/>
     </row>
     <row r="74" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="131" t="s">
-        <v>2</v>
-      </c>
-      <c r="B74" s="95"/>
-      <c r="C74" s="95"/>
-      <c r="D74" s="95"/>
-      <c r="E74" s="95"/>
-      <c r="F74" s="95"/>
-      <c r="G74" s="95"/>
-      <c r="H74" s="95"/>
-      <c r="I74" s="132"/>
+      <c r="A74" s="146" t="s">
+        <v>1</v>
+      </c>
+      <c r="B74" s="147"/>
+      <c r="C74" s="147"/>
+      <c r="D74" s="147"/>
+      <c r="E74" s="147"/>
+      <c r="F74" s="147"/>
+      <c r="G74" s="147"/>
+      <c r="H74" s="147"/>
+      <c r="I74" s="148"/>
       <c r="J74" s="19"/>
     </row>
     <row r="75" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="133" t="s">
-        <v>25</v>
+      <c r="A75" s="72" t="s">
+        <v>22</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -4043,13 +3850,13 @@
       <c r="E75" s="2"/>
       <c r="F75" s="2"/>
       <c r="G75" s="3"/>
-      <c r="H75" s="79"/>
-      <c r="I75" s="134"/>
+      <c r="H75" s="137"/>
+      <c r="I75" s="125"/>
       <c r="J75" s="19"/>
     </row>
     <row r="76" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="135" t="s">
-        <v>39</v>
+      <c r="A76" s="73" t="s">
+        <v>36</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -4057,13 +3864,13 @@
       <c r="E76" s="2"/>
       <c r="F76" s="2"/>
       <c r="G76" s="3"/>
-      <c r="H76" s="72"/>
-      <c r="I76" s="136"/>
+      <c r="H76" s="132"/>
+      <c r="I76" s="121"/>
       <c r="J76" s="19"/>
     </row>
     <row r="77" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="133" t="s">
-        <v>40</v>
+      <c r="A77" s="72" t="s">
+        <v>37</v>
       </c>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -4071,131 +3878,131 @@
       <c r="E77" s="14"/>
       <c r="F77" s="14"/>
       <c r="G77" s="6"/>
-      <c r="H77" s="75"/>
-      <c r="I77" s="137"/>
+      <c r="H77" s="122"/>
+      <c r="I77" s="123"/>
       <c r="J77" s="19"/>
     </row>
     <row r="78" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="138" t="s">
-        <v>3</v>
-      </c>
-      <c r="B78" s="74"/>
-      <c r="C78" s="74"/>
-      <c r="D78" s="74"/>
-      <c r="E78" s="74"/>
-      <c r="F78" s="74"/>
-      <c r="G78" s="74"/>
-      <c r="H78" s="74"/>
-      <c r="I78" s="139"/>
+      <c r="A78" s="126" t="s">
+        <v>2</v>
+      </c>
+      <c r="B78" s="127"/>
+      <c r="C78" s="127"/>
+      <c r="D78" s="127"/>
+      <c r="E78" s="127"/>
+      <c r="F78" s="127"/>
+      <c r="G78" s="127"/>
+      <c r="H78" s="127"/>
+      <c r="I78" s="128"/>
       <c r="J78" s="19"/>
     </row>
     <row r="79" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="140" t="s">
-        <v>38</v>
+      <c r="A79" s="74" t="s">
+        <v>35</v>
       </c>
       <c r="B79" s="7"/>
       <c r="C79" s="7"/>
       <c r="D79" s="15"/>
       <c r="E79" s="16"/>
       <c r="F79" s="14"/>
-      <c r="G79" s="113" t="s">
-        <v>47</v>
-      </c>
-      <c r="H79" s="70"/>
+      <c r="G79" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="H79" s="150"/>
       <c r="I79" s="130"/>
       <c r="J79" s="19"/>
     </row>
     <row r="80" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="141"/>
+      <c r="A80" s="75"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
       <c r="D80" s="13"/>
-      <c r="E80" s="110"/>
-      <c r="F80" s="107"/>
-      <c r="G80" s="112" t="s">
-        <v>46</v>
-      </c>
-      <c r="H80" s="70"/>
+      <c r="E80" s="16"/>
+      <c r="F80" s="14"/>
+      <c r="G80" s="61" t="s">
+        <v>41</v>
+      </c>
+      <c r="H80" s="150"/>
       <c r="I80" s="130"/>
       <c r="J80" s="19"/>
     </row>
     <row r="81" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="180" t="s">
-        <v>31</v>
+      <c r="A81" s="101" t="s">
+        <v>28</v>
       </c>
       <c r="B81" s="20"/>
       <c r="C81" s="20"/>
-      <c r="D81" s="52"/>
-      <c r="E81" s="55"/>
-      <c r="F81" s="53"/>
-      <c r="G81" s="113" t="s">
-        <v>47</v>
-      </c>
-      <c r="H81" s="84"/>
-      <c r="I81" s="184"/>
+      <c r="D81" s="49"/>
+      <c r="E81" s="51"/>
+      <c r="F81" s="50"/>
+      <c r="G81" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="H81" s="118"/>
+      <c r="I81" s="119"/>
       <c r="J81" s="19"/>
     </row>
     <row r="82" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="168"/>
+      <c r="A82" s="93"/>
       <c r="B82" s="17"/>
       <c r="C82" s="17"/>
       <c r="D82" s="18"/>
-      <c r="E82" s="108"/>
-      <c r="F82" s="109"/>
-      <c r="G82" s="112" t="s">
-        <v>46</v>
-      </c>
-      <c r="H82" s="86"/>
-      <c r="I82" s="144"/>
+      <c r="E82" s="59"/>
+      <c r="F82" s="60"/>
+      <c r="G82" s="61" t="s">
+        <v>41</v>
+      </c>
+      <c r="H82" s="165"/>
+      <c r="I82" s="117"/>
       <c r="J82" s="19"/>
     </row>
     <row r="83" spans="1:10" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="179" t="s">
-        <v>32</v>
+      <c r="A83" s="100" t="s">
+        <v>29</v>
       </c>
       <c r="B83" s="7"/>
       <c r="C83" s="7"/>
       <c r="D83" s="15"/>
       <c r="E83" s="16"/>
       <c r="F83" s="14"/>
-      <c r="G83" s="113" t="s">
-        <v>47</v>
-      </c>
-      <c r="H83" s="70"/>
+      <c r="G83" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="H83" s="150"/>
       <c r="I83" s="130"/>
       <c r="J83" s="19"/>
     </row>
     <row r="84" spans="1:10" ht="14.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="141"/>
+      <c r="A84" s="75"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
       <c r="D84" s="13"/>
-      <c r="E84" s="65"/>
-      <c r="F84" s="66"/>
-      <c r="G84" s="112" t="s">
-        <v>46</v>
-      </c>
-      <c r="H84" s="70"/>
+      <c r="E84" s="174"/>
+      <c r="F84" s="169"/>
+      <c r="G84" s="61" t="s">
+        <v>41</v>
+      </c>
+      <c r="H84" s="150"/>
       <c r="I84" s="130"/>
       <c r="J84" s="19"/>
     </row>
     <row r="85" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="145" t="s">
-        <v>4</v>
-      </c>
-      <c r="B85" s="80"/>
-      <c r="C85" s="80"/>
-      <c r="D85" s="80"/>
-      <c r="E85" s="80"/>
-      <c r="F85" s="80"/>
-      <c r="G85" s="80"/>
-      <c r="H85" s="80"/>
-      <c r="I85" s="146"/>
+      <c r="A85" s="166" t="s">
+        <v>3</v>
+      </c>
+      <c r="B85" s="167"/>
+      <c r="C85" s="167"/>
+      <c r="D85" s="167"/>
+      <c r="E85" s="167"/>
+      <c r="F85" s="167"/>
+      <c r="G85" s="167"/>
+      <c r="H85" s="167"/>
+      <c r="I85" s="168"/>
       <c r="J85" s="19"/>
     </row>
     <row r="86" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="185" t="s">
-        <v>45</v>
+      <c r="A86" s="103" t="s">
+        <v>40</v>
       </c>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -4204,12 +4011,12 @@
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
       <c r="H86" s="8"/>
-      <c r="I86" s="148"/>
+      <c r="I86" s="78"/>
       <c r="J86" s="19"/>
     </row>
     <row r="87" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="150" t="s">
-        <v>37</v>
+      <c r="A87" s="80" t="s">
+        <v>34</v>
       </c>
       <c r="B87" s="9"/>
       <c r="C87" s="9"/>
@@ -4217,57 +4024,59 @@
       <c r="E87" s="10"/>
       <c r="F87" s="10"/>
       <c r="G87" s="11"/>
-      <c r="H87" s="72"/>
-      <c r="I87" s="136"/>
+      <c r="H87" s="132"/>
+      <c r="I87" s="121"/>
       <c r="J87" s="19"/>
     </row>
     <row r="88" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="150" t="s">
-        <v>36</v>
+      <c r="A88" s="80" t="s">
+        <v>33</v>
       </c>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
       <c r="D88" s="3"/>
-      <c r="E88" s="72"/>
-      <c r="F88" s="91"/>
-      <c r="G88" s="57" t="s">
-        <v>5</v>
-      </c>
-      <c r="H88" s="72"/>
-      <c r="I88" s="136"/>
+      <c r="E88" s="132"/>
+      <c r="F88" s="133"/>
+      <c r="G88" s="52" t="s">
+        <v>4</v>
+      </c>
+      <c r="H88" s="132"/>
+      <c r="I88" s="121"/>
       <c r="J88" s="19"/>
     </row>
     <row r="89" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="181" t="s">
-        <v>44</v>
-      </c>
-      <c r="B89" s="28"/>
-      <c r="C89" s="28"/>
-      <c r="D89" s="28"/>
-      <c r="E89" s="29"/>
-      <c r="F89" s="56"/>
-      <c r="G89" s="63" t="s">
-        <v>42</v>
-      </c>
-      <c r="H89" s="96"/>
-      <c r="I89" s="172"/>
+      <c r="A89" s="105" t="s">
+        <v>39</v>
+      </c>
+      <c r="B89" s="81"/>
+      <c r="C89" s="81"/>
+      <c r="D89" s="81"/>
+      <c r="E89" s="82"/>
+      <c r="F89" s="180" t="s">
+        <v>46</v>
+      </c>
+      <c r="G89" s="181" t="s">
+        <v>45</v>
+      </c>
+      <c r="H89" s="157"/>
+      <c r="I89" s="158"/>
       <c r="J89" s="19"/>
     </row>
     <row r="90" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="175"/>
-      <c r="B90" s="158"/>
-      <c r="C90" s="158"/>
-      <c r="D90" s="158"/>
-      <c r="E90" s="158"/>
-      <c r="F90" s="163"/>
-      <c r="G90" s="164"/>
-      <c r="H90" s="165"/>
-      <c r="I90" s="176"/>
+      <c r="A90" s="96"/>
+      <c r="B90" s="83"/>
+      <c r="C90" s="83"/>
+      <c r="D90" s="83"/>
+      <c r="E90" s="83"/>
+      <c r="F90" s="88"/>
+      <c r="G90" s="89"/>
+      <c r="H90" s="90"/>
+      <c r="I90" s="97"/>
       <c r="J90" s="19"/>
     </row>
     <row r="91" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="182" t="s">
-        <v>22</v>
+      <c r="A91" s="102" t="s">
+        <v>19</v>
       </c>
       <c r="B91" s="22"/>
       <c r="C91" s="23"/>
@@ -4277,43 +4086,45 @@
       <c r="G91" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="H91" s="51"/>
-      <c r="I91" s="178"/>
+      <c r="H91" s="48"/>
+      <c r="I91" s="99"/>
       <c r="J91" s="19"/>
     </row>
     <row r="92" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="129" t="s">
-        <v>41</v>
-      </c>
-      <c r="B92" s="97"/>
-      <c r="C92" s="83"/>
-      <c r="D92" s="98"/>
-      <c r="E92" s="92" t="s">
+      <c r="A92" s="178" t="s">
         <v>43</v>
       </c>
-      <c r="F92" s="93"/>
-      <c r="G92" s="94"/>
-      <c r="H92" s="83"/>
-      <c r="I92" s="137"/>
+      <c r="B92" s="179" t="s">
+        <v>44</v>
+      </c>
+      <c r="C92" s="122"/>
+      <c r="D92" s="141"/>
+      <c r="E92" s="138" t="s">
+        <v>38</v>
+      </c>
+      <c r="F92" s="139"/>
+      <c r="G92" s="140"/>
+      <c r="H92" s="122"/>
+      <c r="I92" s="123"/>
       <c r="J92" s="19"/>
     </row>
     <row r="93" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="131" t="s">
-        <v>2</v>
-      </c>
-      <c r="B93" s="95"/>
-      <c r="C93" s="95"/>
-      <c r="D93" s="95"/>
-      <c r="E93" s="95"/>
-      <c r="F93" s="95"/>
-      <c r="G93" s="95"/>
-      <c r="H93" s="95"/>
-      <c r="I93" s="132"/>
+      <c r="A93" s="146" t="s">
+        <v>1</v>
+      </c>
+      <c r="B93" s="147"/>
+      <c r="C93" s="147"/>
+      <c r="D93" s="147"/>
+      <c r="E93" s="147"/>
+      <c r="F93" s="147"/>
+      <c r="G93" s="147"/>
+      <c r="H93" s="147"/>
+      <c r="I93" s="148"/>
       <c r="J93" s="19"/>
     </row>
     <row r="94" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="133" t="s">
-        <v>25</v>
+      <c r="A94" s="72" t="s">
+        <v>22</v>
       </c>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -4321,13 +4132,13 @@
       <c r="E94" s="2"/>
       <c r="F94" s="2"/>
       <c r="G94" s="3"/>
-      <c r="H94" s="78"/>
-      <c r="I94" s="134"/>
+      <c r="H94" s="124"/>
+      <c r="I94" s="125"/>
       <c r="J94" s="19"/>
     </row>
     <row r="95" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="135" t="s">
-        <v>7</v>
+      <c r="A95" s="73" t="s">
+        <v>5</v>
       </c>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -4335,145 +4146,145 @@
       <c r="E95" s="2"/>
       <c r="F95" s="2"/>
       <c r="G95" s="3"/>
-      <c r="H95" s="83"/>
-      <c r="I95" s="137"/>
+      <c r="H95" s="151"/>
+      <c r="I95" s="123"/>
       <c r="J95" s="19"/>
     </row>
     <row r="96" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="133" t="s">
-        <v>23</v>
+      <c r="A96" s="72" t="s">
+        <v>20</v>
       </c>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
       <c r="D96" s="4"/>
       <c r="E96" s="14"/>
       <c r="F96" s="14"/>
-      <c r="G96" s="58"/>
-      <c r="H96" s="76"/>
-      <c r="I96" s="186"/>
+      <c r="G96" s="53"/>
+      <c r="H96" s="170"/>
+      <c r="I96" s="171"/>
       <c r="J96" s="19"/>
     </row>
     <row r="97" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="187" t="s">
-        <v>3</v>
-      </c>
-      <c r="B97" s="88"/>
-      <c r="C97" s="88"/>
-      <c r="D97" s="88"/>
-      <c r="E97" s="88"/>
-      <c r="F97" s="88"/>
-      <c r="G97" s="88"/>
-      <c r="H97" s="88"/>
-      <c r="I97" s="188"/>
+      <c r="A97" s="159" t="s">
+        <v>2</v>
+      </c>
+      <c r="B97" s="160"/>
+      <c r="C97" s="160"/>
+      <c r="D97" s="160"/>
+      <c r="E97" s="160"/>
+      <c r="F97" s="160"/>
+      <c r="G97" s="160"/>
+      <c r="H97" s="160"/>
+      <c r="I97" s="161"/>
       <c r="J97" s="19"/>
     </row>
     <row r="98" spans="1:10" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="180" t="s">
-        <v>38</v>
+      <c r="A98" s="101" t="s">
+        <v>35</v>
       </c>
       <c r="B98" s="20"/>
       <c r="C98" s="20"/>
-      <c r="D98" s="52"/>
-      <c r="E98" s="53"/>
-      <c r="F98" s="53"/>
-      <c r="G98" s="113" t="s">
-        <v>47</v>
-      </c>
-      <c r="H98" s="69"/>
-      <c r="I98" s="170"/>
+      <c r="D98" s="49"/>
+      <c r="E98" s="50"/>
+      <c r="F98" s="50"/>
+      <c r="G98" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="H98" s="153"/>
+      <c r="I98" s="154"/>
       <c r="J98" s="19"/>
     </row>
     <row r="99" spans="1:10" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="141"/>
+      <c r="A99" s="75"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
       <c r="D99" s="13"/>
-      <c r="E99" s="66"/>
-      <c r="F99" s="66"/>
-      <c r="G99" s="112" t="s">
-        <v>46</v>
-      </c>
-      <c r="H99" s="81"/>
+      <c r="E99" s="169"/>
+      <c r="F99" s="169"/>
+      <c r="G99" s="61" t="s">
+        <v>41</v>
+      </c>
+      <c r="H99" s="152"/>
       <c r="I99" s="130"/>
       <c r="J99" s="19"/>
     </row>
     <row r="100" spans="1:10" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="180" t="s">
-        <v>31</v>
+      <c r="A100" s="101" t="s">
+        <v>28</v>
       </c>
       <c r="B100" s="20"/>
       <c r="C100" s="20"/>
-      <c r="D100" s="52"/>
-      <c r="E100" s="53"/>
-      <c r="F100" s="53"/>
-      <c r="G100" s="113" t="s">
-        <v>47</v>
-      </c>
-      <c r="H100" s="69"/>
-      <c r="I100" s="170"/>
+      <c r="D100" s="49"/>
+      <c r="E100" s="50"/>
+      <c r="F100" s="50"/>
+      <c r="G100" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="H100" s="153"/>
+      <c r="I100" s="154"/>
       <c r="J100" s="19"/>
     </row>
     <row r="101" spans="1:10" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="168"/>
+      <c r="A101" s="93"/>
       <c r="B101" s="17"/>
       <c r="C101" s="17"/>
       <c r="D101" s="18"/>
-      <c r="E101" s="67"/>
-      <c r="F101" s="67"/>
-      <c r="G101" s="112" t="s">
-        <v>46</v>
-      </c>
-      <c r="H101" s="68"/>
-      <c r="I101" s="144"/>
+      <c r="E101" s="175"/>
+      <c r="F101" s="175"/>
+      <c r="G101" s="61" t="s">
+        <v>41</v>
+      </c>
+      <c r="H101" s="116"/>
+      <c r="I101" s="117"/>
       <c r="J101" s="19"/>
     </row>
     <row r="102" spans="1:10" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="179" t="s">
-        <v>32</v>
+      <c r="A102" s="100" t="s">
+        <v>29</v>
       </c>
       <c r="B102" s="7"/>
       <c r="C102" s="7"/>
       <c r="D102" s="15"/>
       <c r="E102" s="14"/>
       <c r="F102" s="14"/>
-      <c r="G102" s="113" t="s">
-        <v>47</v>
-      </c>
-      <c r="H102" s="68"/>
-      <c r="I102" s="144"/>
+      <c r="G102" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="H102" s="116"/>
+      <c r="I102" s="117"/>
       <c r="J102" s="19"/>
     </row>
     <row r="103" spans="1:10" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="179"/>
+      <c r="A103" s="100"/>
       <c r="B103" s="7"/>
       <c r="C103" s="7"/>
       <c r="D103" s="15"/>
       <c r="E103" s="14"/>
       <c r="F103" s="14"/>
-      <c r="G103" s="112" t="s">
-        <v>46</v>
-      </c>
-      <c r="H103" s="68"/>
-      <c r="I103" s="144"/>
+      <c r="G103" s="61" t="s">
+        <v>41</v>
+      </c>
+      <c r="H103" s="116"/>
+      <c r="I103" s="117"/>
       <c r="J103" s="19"/>
     </row>
     <row r="104" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="189" t="s">
-        <v>4</v>
-      </c>
-      <c r="B104" s="89"/>
-      <c r="C104" s="89"/>
-      <c r="D104" s="89"/>
-      <c r="E104" s="89"/>
-      <c r="F104" s="89"/>
-      <c r="G104" s="89"/>
-      <c r="H104" s="89"/>
-      <c r="I104" s="190"/>
+      <c r="A104" s="162" t="s">
+        <v>3</v>
+      </c>
+      <c r="B104" s="163"/>
+      <c r="C104" s="163"/>
+      <c r="D104" s="163"/>
+      <c r="E104" s="163"/>
+      <c r="F104" s="163"/>
+      <c r="G104" s="163"/>
+      <c r="H104" s="163"/>
+      <c r="I104" s="164"/>
       <c r="J104" s="19"/>
     </row>
     <row r="105" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="191" t="s">
-        <v>24</v>
+      <c r="A105" s="104" t="s">
+        <v>21</v>
       </c>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
@@ -4482,12 +4293,12 @@
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
       <c r="H105" s="8"/>
-      <c r="I105" s="148"/>
+      <c r="I105" s="78"/>
       <c r="J105" s="19"/>
     </row>
     <row r="106" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="150" t="s">
-        <v>33</v>
+      <c r="A106" s="80" t="s">
+        <v>30</v>
       </c>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -4495,40 +4306,42 @@
       <c r="E106" s="8"/>
       <c r="F106" s="8"/>
       <c r="G106" s="3"/>
-      <c r="H106" s="90"/>
-      <c r="I106" s="136"/>
+      <c r="H106" s="120"/>
+      <c r="I106" s="121"/>
       <c r="J106" s="19"/>
     </row>
     <row r="107" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="149" t="s">
-        <v>36</v>
+      <c r="A107" s="79" t="s">
+        <v>33</v>
       </c>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
       <c r="D107" s="3"/>
-      <c r="E107" s="90"/>
-      <c r="F107" s="91"/>
-      <c r="G107" s="57" t="s">
-        <v>5</v>
-      </c>
-      <c r="H107" s="90"/>
-      <c r="I107" s="136"/>
+      <c r="E107" s="120"/>
+      <c r="F107" s="133"/>
+      <c r="G107" s="52" t="s">
+        <v>4</v>
+      </c>
+      <c r="H107" s="120"/>
+      <c r="I107" s="121"/>
       <c r="J107" s="19"/>
     </row>
-    <row r="108" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="192" t="s">
-        <v>44</v>
-      </c>
-      <c r="B108" s="152"/>
-      <c r="C108" s="152"/>
-      <c r="D108" s="152"/>
-      <c r="E108" s="153"/>
-      <c r="F108" s="193"/>
-      <c r="G108" s="155" t="s">
-        <v>42</v>
-      </c>
-      <c r="H108" s="194"/>
-      <c r="I108" s="157"/>
+    <row r="108" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A108" s="105" t="s">
+        <v>39</v>
+      </c>
+      <c r="B108" s="81"/>
+      <c r="C108" s="81"/>
+      <c r="D108" s="81"/>
+      <c r="E108" s="82"/>
+      <c r="F108" s="180" t="s">
+        <v>46</v>
+      </c>
+      <c r="G108" s="181" t="s">
+        <v>45</v>
+      </c>
+      <c r="H108" s="157"/>
+      <c r="I108" s="158"/>
       <c r="J108" s="19"/>
     </row>
     <row r="109" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -4543,70 +4356,30 @@
       <c r="I109" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="109">
-    <mergeCell ref="H103:I103"/>
-    <mergeCell ref="H81:I81"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="H57:I57"/>
-    <mergeCell ref="H73:I73"/>
-    <mergeCell ref="H56:I56"/>
-    <mergeCell ref="A59:I59"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="E62:F62"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="A17:I17"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:I21"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="A36:I36"/>
-    <mergeCell ref="E35:G35"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="H80:I80"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="E54:G54"/>
-    <mergeCell ref="H58:I58"/>
-    <mergeCell ref="A55:I55"/>
-    <mergeCell ref="H68:I68"/>
-    <mergeCell ref="E73:G73"/>
-    <mergeCell ref="A74:I74"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="H70:I70"/>
-    <mergeCell ref="H65:I65"/>
-    <mergeCell ref="H64:I64"/>
-    <mergeCell ref="H62:I62"/>
-    <mergeCell ref="H61:I61"/>
-    <mergeCell ref="H63:I63"/>
-    <mergeCell ref="H37:I37"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="H108:I108"/>
-    <mergeCell ref="A97:I97"/>
-    <mergeCell ref="A104:I104"/>
-    <mergeCell ref="E107:F107"/>
-    <mergeCell ref="H107:I107"/>
-    <mergeCell ref="H82:I82"/>
-    <mergeCell ref="E92:G92"/>
-    <mergeCell ref="A93:I93"/>
-    <mergeCell ref="H94:I94"/>
-    <mergeCell ref="H89:I89"/>
-    <mergeCell ref="A85:I85"/>
-    <mergeCell ref="E88:F88"/>
-    <mergeCell ref="H88:I88"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="H95:I95"/>
-    <mergeCell ref="E99:F99"/>
-    <mergeCell ref="H99:I99"/>
-    <mergeCell ref="H102:I102"/>
+  <mergeCells count="104">
+    <mergeCell ref="J46:K46"/>
+    <mergeCell ref="J48:K48"/>
+    <mergeCell ref="J49:K49"/>
+    <mergeCell ref="J47:K47"/>
+    <mergeCell ref="E101:F101"/>
+    <mergeCell ref="H101:I101"/>
+    <mergeCell ref="H98:I98"/>
+    <mergeCell ref="H83:I83"/>
+    <mergeCell ref="E84:F84"/>
+    <mergeCell ref="H84:I84"/>
+    <mergeCell ref="H76:I76"/>
+    <mergeCell ref="A78:I78"/>
+    <mergeCell ref="H77:I77"/>
+    <mergeCell ref="H87:I87"/>
+    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="H69:I69"/>
+    <mergeCell ref="H79:I79"/>
+    <mergeCell ref="H75:I75"/>
+    <mergeCell ref="A66:I66"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="H51:I51"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="H54:I54"/>
     <mergeCell ref="H100:I100"/>
     <mergeCell ref="H106:I106"/>
     <mergeCell ref="H92:I92"/>
@@ -4630,29 +4403,64 @@
     <mergeCell ref="A47:I47"/>
     <mergeCell ref="A28:I28"/>
     <mergeCell ref="C35:D35"/>
-    <mergeCell ref="J46:K46"/>
-    <mergeCell ref="J48:K48"/>
-    <mergeCell ref="J49:K49"/>
-    <mergeCell ref="J47:K47"/>
-    <mergeCell ref="E101:F101"/>
-    <mergeCell ref="H101:I101"/>
-    <mergeCell ref="H98:I98"/>
-    <mergeCell ref="H83:I83"/>
-    <mergeCell ref="E84:F84"/>
-    <mergeCell ref="H84:I84"/>
-    <mergeCell ref="H76:I76"/>
-    <mergeCell ref="A78:I78"/>
-    <mergeCell ref="H77:I77"/>
-    <mergeCell ref="H87:I87"/>
-    <mergeCell ref="E69:F69"/>
-    <mergeCell ref="H69:I69"/>
-    <mergeCell ref="H79:I79"/>
-    <mergeCell ref="H75:I75"/>
-    <mergeCell ref="A66:I66"/>
-    <mergeCell ref="H60:I60"/>
-    <mergeCell ref="H51:I51"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="H54:I54"/>
+    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="H61:I61"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="H108:I108"/>
+    <mergeCell ref="A97:I97"/>
+    <mergeCell ref="A104:I104"/>
+    <mergeCell ref="E107:F107"/>
+    <mergeCell ref="H107:I107"/>
+    <mergeCell ref="H82:I82"/>
+    <mergeCell ref="E92:G92"/>
+    <mergeCell ref="A93:I93"/>
+    <mergeCell ref="H94:I94"/>
+    <mergeCell ref="H89:I89"/>
+    <mergeCell ref="A85:I85"/>
+    <mergeCell ref="E88:F88"/>
+    <mergeCell ref="H88:I88"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="H95:I95"/>
+    <mergeCell ref="E99:F99"/>
+    <mergeCell ref="H99:I99"/>
+    <mergeCell ref="H102:I102"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="H103:I103"/>
+    <mergeCell ref="H81:I81"/>
+    <mergeCell ref="H57:I57"/>
+    <mergeCell ref="H73:I73"/>
+    <mergeCell ref="H56:I56"/>
+    <mergeCell ref="A59:I59"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="A36:I36"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="H80:I80"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="E54:G54"/>
+    <mergeCell ref="H58:I58"/>
+    <mergeCell ref="A55:I55"/>
+    <mergeCell ref="H68:I68"/>
+    <mergeCell ref="E73:G73"/>
+    <mergeCell ref="A74:I74"/>
+    <mergeCell ref="H70:I70"/>
+    <mergeCell ref="H65:I65"/>
+    <mergeCell ref="H64:I64"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
